--- a/AAII_Financials/Yearly/SCOR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SCOR_YR_FIN.xlsx
@@ -3023,10 +3023,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>58200</v>
+        <v>48500</v>
       </c>
       <c r="E59" s="3">
-        <v>79800</v>
+        <v>71600</v>
       </c>
       <c r="F59" s="3">
         <v>95200</v>
